--- a/ITI/MHD/StructureDefinition-IHE.MHD.List.xlsx
+++ b/ITI/MHD/StructureDefinition-IHE.MHD.List.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1099" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1133" uniqueCount="295">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>4.2.3</t>
+    <t>4.2.4</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-31T14:38:46-05:00</t>
+    <t>2026-06-15T14:55:16-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -466,6 +466,22 @@
   <si>
     <t xml:space="preserve">ele-1
 </t>
+  </si>
+  <si>
+    <t>List.extension:homeCommunityId</t>
+  </si>
+  <si>
+    <t>homeCommunityId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://profiles.ihe.net/ITI/MHD/StructureDefinition/ihe-HomeCommunityId}
+</t>
+  </si>
+  <si>
+    <t>The homeCommunityId where the artifact resides</t>
+  </si>
+  <si>
+    <t>The globally unique, immutable, identifier of the homeCommunityId entity where this artifact resides. The format of the value is an OID.</t>
   </si>
   <si>
     <t>List.modifierExtension</t>
@@ -1235,12 +1251,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL31"/>
+  <dimension ref="A1:AL32"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="25.703125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="27.98046875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="23.53125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="14.1484375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="16.421875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.8125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.29296875" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.21484375" customWidth="true" bestFit="true"/>
@@ -1248,7 +1264,7 @@
     <col min="8" max="8" width="13.1171875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="10.75390625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="69.65625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="72.125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2362,9 +2378,11 @@
         <v>145</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="C11" s="2"/>
+        <v>131</v>
+      </c>
+      <c r="C11" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="D11" t="s" s="2">
         <v>80</v>
       </c>
@@ -2373,25 +2391,25 @@
         <v>78</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="J11" t="s" s="2">
         <v>80</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2442,7 +2460,7 @@
         <v>80</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -2451,7 +2469,7 @@
         <v>79</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>80</v>
+        <v>144</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>138</v>
@@ -2465,10 +2483,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2479,25 +2497,25 @@
         <v>78</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="J12" t="s" s="2">
         <v>80</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>148</v>
+        <v>132</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2548,7 +2566,7 @@
         <v>80</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -2560,21 +2578,21 @@
         <v>80</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>151</v>
+        <v>80</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>152</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2582,22 +2600,22 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>107</v>
+        <v>153</v>
       </c>
       <c r="L13" t="s" s="2">
         <v>154</v>
@@ -2605,9 +2623,7 @@
       <c r="M13" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="N13" t="s" s="2">
-        <v>156</v>
-      </c>
+      <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>80</v>
@@ -2632,13 +2648,13 @@
         <v>80</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>157</v>
+        <v>80</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>158</v>
+        <v>80</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>159</v>
+        <v>80</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>80</v>
@@ -2656,13 +2672,13 @@
         <v>80</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>80</v>
@@ -2671,18 +2687,18 @@
         <v>99</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>161</v>
+        <v>157</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2708,17 +2724,15 @@
         <v>107</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>166</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>80</v>
       </c>
@@ -2742,13 +2756,13 @@
         <v>80</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>80</v>
@@ -2766,7 +2780,7 @@
         <v>80</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>87</v>
@@ -2781,18 +2795,18 @@
         <v>99</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2800,7 +2814,7 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>87</v>
@@ -2809,23 +2823,25 @@
         <v>80</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="J15" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>172</v>
+        <v>107</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N15" s="2"/>
+        <v>169</v>
+      </c>
+      <c r="N15" t="s" s="2">
+        <v>170</v>
+      </c>
       <c r="O15" t="s" s="2">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>80</v>
@@ -2838,7 +2854,7 @@
         <v>80</v>
       </c>
       <c r="T15" t="s" s="2">
-        <v>176</v>
+        <v>80</v>
       </c>
       <c r="U15" t="s" s="2">
         <v>80</v>
@@ -2850,13 +2866,13 @@
         <v>80</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>80</v>
+        <v>162</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>80</v>
+        <v>172</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>80</v>
+        <v>173</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>80</v>
@@ -2874,10 +2890,10 @@
         <v>80</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH15" t="s" s="2">
         <v>87</v>
@@ -2889,18 +2905,18 @@
         <v>99</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>80</v>
+        <v>175</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2908,7 +2924,7 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>87</v>
@@ -2923,19 +2939,17 @@
         <v>88</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="M16" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="N16" s="2"/>
+      <c r="O16" t="s" s="2">
         <v>180</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>183</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>80</v>
@@ -2948,7 +2962,7 @@
         <v>80</v>
       </c>
       <c r="T16" t="s" s="2">
-        <v>80</v>
+        <v>181</v>
       </c>
       <c r="U16" t="s" s="2">
         <v>80</v>
@@ -2960,11 +2974,13 @@
         <v>80</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="Y16" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="Y16" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="Z16" t="s" s="2">
-        <v>184</v>
+        <v>80</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>80</v>
@@ -2982,7 +2998,7 @@
         <v>80</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -2997,18 +3013,18 @@
         <v>99</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>186</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3016,7 +3032,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>87</v>
@@ -3031,19 +3047,19 @@
         <v>88</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="M17" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="O17" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="L17" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>192</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>80</v>
@@ -3068,13 +3084,11 @@
         <v>80</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y17" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="Y17" s="2"/>
       <c r="Z17" t="s" s="2">
-        <v>80</v>
+        <v>189</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>80</v>
@@ -3092,7 +3106,7 @@
         <v>80</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3107,18 +3121,18 @@
         <v>99</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>194</v>
+        <v>191</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3138,19 +3152,23 @@
         <v>80</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="L18" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="M18" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="N18" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="O18" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="M18" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="N18" s="2"/>
-      <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>80</v>
       </c>
@@ -3198,7 +3216,7 @@
         <v>80</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3213,18 +3231,18 @@
         <v>99</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="AL18" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="AL18" t="s" s="2">
-        <v>200</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3244,23 +3262,19 @@
         <v>80</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="M19" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>206</v>
-      </c>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>80</v>
       </c>
@@ -3308,7 +3322,7 @@
         <v>80</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3323,22 +3337,22 @@
         <v>99</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>210</v>
+        <v>80</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -3357,19 +3371,19 @@
         <v>88</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="M20" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="O20" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="L20" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>80</v>
@@ -3418,7 +3432,7 @@
         <v>80</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3433,22 +3447,22 @@
         <v>99</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>217</v>
+        <v>213</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>80</v>
+        <v>215</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -3464,22 +3478,22 @@
         <v>80</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>179</v>
+        <v>216</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="N21" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="O21" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>222</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>80</v>
@@ -3504,13 +3518,13 @@
         <v>80</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>223</v>
+        <v>80</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>224</v>
+        <v>80</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>80</v>
@@ -3528,7 +3542,7 @@
         <v>80</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -3543,18 +3557,18 @@
         <v>99</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>80</v>
+        <v>222</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3565,7 +3579,7 @@
         <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>80</v>
@@ -3577,16 +3591,20 @@
         <v>80</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="L22" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="M22" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="O22" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="L22" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="N22" s="2"/>
-      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>80</v>
       </c>
@@ -3610,13 +3628,13 @@
         <v>80</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>80</v>
+        <v>111</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>80</v>
+        <v>228</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>80</v>
+        <v>229</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>80</v>
@@ -3634,13 +3652,13 @@
         <v>80</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>80</v>
@@ -3691,9 +3709,7 @@
       <c r="M23" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="N23" t="s" s="2">
-        <v>235</v>
-      </c>
+      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>80</v>
@@ -3751,13 +3767,13 @@
         <v>79</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>236</v>
+        <v>80</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>80</v>
@@ -3765,10 +3781,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3779,7 +3795,7 @@
         <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>80</v>
@@ -3791,15 +3807,17 @@
         <v>80</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>172</v>
+        <v>237</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>80</v>
@@ -3848,19 +3866,19 @@
         <v>80</v>
       </c>
       <c r="AF24" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="AG24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH24" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI24" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="AG24" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH24" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI24" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="AJ24" t="s" s="2">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>242</v>
@@ -3878,14 +3896,14 @@
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>244</v>
+        <v>80</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>80</v>
@@ -3897,17 +3915,15 @@
         <v>80</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>132</v>
+        <v>177</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="M25" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>247</v>
-      </c>
+      <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>80</v>
@@ -3956,22 +3972,22 @@
         <v>80</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>138</v>
+        <v>80</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>80</v>
@@ -3979,14 +3995,14 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -3999,26 +4015,24 @@
         <v>80</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="K26" t="s" s="2">
         <v>132</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="N26" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>253</v>
-      </c>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>80</v>
       </c>
@@ -4066,7 +4080,7 @@
         <v>80</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4081,7 +4095,7 @@
         <v>138</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>130</v>
+        <v>247</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>80</v>
@@ -4089,33 +4103,33 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>80</v>
+        <v>255</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>179</v>
+        <v>132</v>
       </c>
       <c r="L27" t="s" s="2">
         <v>256</v>
@@ -4124,10 +4138,10 @@
         <v>257</v>
       </c>
       <c r="N27" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="O27" t="s" s="2">
         <v>258</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>259</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>80</v>
@@ -4152,13 +4166,13 @@
         <v>80</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>260</v>
+        <v>80</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>261</v>
+        <v>80</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>262</v>
+        <v>80</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>80</v>
@@ -4176,22 +4190,22 @@
         <v>80</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>169</v>
+        <v>130</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>80</v>
@@ -4199,10 +4213,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4219,59 +4233,57 @@
         <v>80</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="J28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="M28" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="O28" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="P28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q28" s="2"/>
+      <c r="R28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X28" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="Y28" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="N28" t="s" s="2">
+      <c r="Z28" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="O28" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="P28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q28" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="R28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z28" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="AA28" t="s" s="2">
         <v>80</v>
       </c>
@@ -4288,7 +4300,7 @@
         <v>80</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4297,13 +4309,13 @@
         <v>87</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>270</v>
+        <v>80</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>271</v>
+        <v>174</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>80</v>
@@ -4311,10 +4323,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4331,28 +4343,32 @@
         <v>80</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="J29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>202</v>
+        <v>269</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="O29" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="P29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q29" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="N29" s="2"/>
-      <c r="O29" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="P29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q29" s="2"/>
       <c r="R29" t="s" s="2">
         <v>80</v>
       </c>
@@ -4396,7 +4412,7 @@
         <v>80</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4405,7 +4421,7 @@
         <v>87</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>80</v>
+        <v>275</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>99</v>
@@ -4430,7 +4446,7 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>87</v>
@@ -4445,16 +4461,18 @@
         <v>80</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="M30" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" s="2"/>
+      <c r="O30" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>80</v>
       </c>
@@ -4505,7 +4523,7 @@
         <v>277</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH30" t="s" s="2">
         <v>87</v>
@@ -4536,7 +4554,7 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>87</v>
@@ -4551,20 +4569,16 @@
         <v>80</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>179</v>
+        <v>283</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="N31" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="O31" t="s" s="2">
-        <v>286</v>
-      </c>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>80</v>
       </c>
@@ -4588,13 +4602,13 @@
         <v>80</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>287</v>
+        <v>80</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>288</v>
+        <v>80</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>80</v>
@@ -4615,21 +4629,131 @@
         <v>282</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH31" t="s" s="2">
         <v>87</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>236</v>
+        <v>80</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK31" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="C32" s="2"/>
+      <c r="D32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E32" s="2"/>
+      <c r="F32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G32" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K32" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="AL31" t="s" s="2">
+      <c r="N32" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="O32" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="P32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q32" s="2"/>
+      <c r="R32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X32" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="Z32" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="AA32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF32" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="AG32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH32" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI32" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK32" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="AL32" t="s" s="2">
         <v>80</v>
       </c>
     </row>

--- a/ITI/MHD/StructureDefinition-IHE.MHD.List.xlsx
+++ b/ITI/MHD/StructureDefinition-IHE.MHD.List.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>4.2.4</t>
+    <t>4.2.5-comment</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T14:55:16-05:00</t>
+    <t>2026-06-16T19:25:56-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
